--- a/business/investor-pack/scoup-financial-model.xlsx
+++ b/business/investor-pack/scoup-financial-model.xlsx
@@ -2014,12 +2014,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Series B $44M (Sep 2025, led by Base10) at about $500M valuation</t>
+          <t>Series B $44M (3 Sep 2025, led by Base10); valuation not confirmed</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B (round); valuation unconfirmed</t>
         </is>
       </c>
     </row>
@@ -2283,12 +2283,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Cass FY2025 10-K</t>
+          <t>Cass FY2025 results, 8-K exhibit 99.1 (22 Jan 2026)</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/708781/000070878126000010/cass-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/708781/000070878126000002/cass-20251231xexx991.htm</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HappyRobot Series B $44M at about $500M</t>
+          <t>HappyRobot Series B $44M (3 Sep 2025, Base10); valuation NOT confirmed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>VERIFIED secondary</t>
+          <t>Round verified, secondary; valuation unconfirmed</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carrier charges and overcharge actions: 18 months</t>
+          <t>18 months for charges/overcharges (a)-(b); +6 months after written disallowance (d)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>49 U.S.C. 14705(a)-(b)</t>
+          <t>49 U.S.C. 14705(a), (b), (d)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3057,27 +3057,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Assumptions!K21:K28</t>
+          <t>(docs only)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SSB and BLS wage bases</t>
+          <t>Failure to include required D&amp;D invoice information eliminates the obligation to pay</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SSB; BLS Occupational Outlook</t>
+          <t>46 U.S.C. 41104(d)(2), (f)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.ssb.no/arbeid-og-lonn/lonn-og-arbeidskraftkostnader/statistikk/lonn</t>
+          <t>https://www.govinfo.gov/app/details/USCODE-2023-title46</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>2022 (OSRA)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3087,34 +3087,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NOT re-verified this pass; loaded costs remain assumptions (C)</t>
+          <t>VERIFIED primary</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Assumptions!K33</t>
+          <t>Assumptions!K21:K28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SOC 2 Type II $50-110K; pen test $15-35K</t>
+          <t>SSB 2025 ICT NOK 80,770/month; BLS May 2025 medians; employer tax 14.1%</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vendor ranges</t>
+          <t>SSB; BLS Occupational Outlook Handbook; Skatteetaten</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.ssb.no/arbeid-og-lonn/lonn-og-arbeidskraftkostnader/statistikk/lonn</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>various</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3124,42 +3124,79 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>NOT verified; assumption (C)</t>
+          <t>VERIFIED primary; multipliers 1.22 / 1.43 remain assumptions</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Assumptions!K33</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SOC 2 Type II $50-110K; pen test $15-35K</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>vendor ranges</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NOT verified; assumption (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Competitors!C6, C10, C11, C13, C14</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Trax, Terminal49, Vizion, Freightos, Transporeon</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>various</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>NOT re-verified this pass; existing grades kept</t>
         </is>
@@ -3768,7 +3805,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>SSB ICT pay NOK ~969K x 1.22 (A/C)</t>
+          <t>SSB 2025: information and communication NOK 80,770/month (about NOK 969K/yr) x 1.22 loaded (A/C)</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3846,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>SSB ICT pay, upper range, x 1.22 (A/C)</t>
+          <t>SSB 2025 ICT pay, upper range, x 1.22 (A/C)</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3887,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>SSB ICT pay x 1.22; BLS infosec median $129K for US comparison (A)</t>
+          <t>SSB ICT pay x 1.22; BLS May 2025 information security analysts median $129,180 for US comparison (A)</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3928,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>BLS technical sales base $105K, on-target earnings ~2x base, loaded (A/C)</t>
+          <t>BLS May 2025 technical and scientific sales reps median $104,920; on-target earnings ~2x base, loaded (A/C)</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3969,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>BLS sales engineer median $125K x 1.43 (A)</t>
+          <t>BLS May 2025 sales engineers median $124,900 x 1.43 (A)</t>
         </is>
       </c>
     </row>
